--- a/Daten/data_slido.xlsx
+++ b/Daten/data_slido.xlsx
@@ -1,21 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\JEF\SimEP\Daten\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E1FA3FA-0866-4778-A627-51DABAE541E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="7"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Übersicht" sheetId="1" r:id="rId1"/>
+    <sheet name="Übersicht" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -25,88 +20,133 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
-  <si>
-    <t>Stadt</t>
-  </si>
-  <si>
-    <t>EVP</t>
-  </si>
-  <si>
-    <t>SD</t>
-  </si>
-  <si>
-    <t>RE</t>
-  </si>
-  <si>
-    <t>Green</t>
-  </si>
-  <si>
-    <t>PfE</t>
-  </si>
-  <si>
-    <t>Left</t>
-  </si>
-  <si>
-    <t>Ulm</t>
-  </si>
-  <si>
-    <t>www.jef-bayern.de</t>
-  </si>
-  <si>
-    <t>Nürnberg</t>
-  </si>
-  <si>
-    <t>Coburg</t>
-  </si>
-  <si>
-    <t>Passau</t>
-  </si>
-  <si>
-    <t>München</t>
-  </si>
-  <si>
-    <t>https://wall.sli.do/event/5ytbGMXRey7ze9iYr2o1Gx</t>
-  </si>
-  <si>
-    <t>https://wall.sli.do/event/cGu8QCMc789wmmh8Vc2Fya</t>
-  </si>
-  <si>
-    <t>https://wall.sli.do/event/trwYxNkvGPU4wB6QdQKYUQ</t>
-  </si>
-  <si>
-    <t>https://wall.sli.do/event/eHfbbWUUfx46oVaXFytCFZ</t>
-  </si>
-  <si>
-    <t>https://wall.sli.do/event/dtWESWtajaF2nmnxngxbg4</t>
-  </si>
-  <si>
-    <t>https://wall.sli.do/event/obRbSvykRMTii7BHz5Kdxj</t>
-  </si>
-  <si>
-    <t>https://wall.sli.do/event/igq3HyvzFLzkZURA7ceLCC</t>
-  </si>
-  <si>
-    <t>https://wall.sli.do/event/geV2Mhwjr214EoiLePvBLu</t>
-  </si>
-  <si>
-    <t>https://wall.sli.do/event/gtxWrkTKz8if2RfFpJ69xd</t>
-  </si>
-  <si>
-    <t>https://wall.sli.do/event/tFRDNiRPzWnazRZebU57n1</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+  <si>
+    <t xml:space="preserve">Stadt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PfE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ulm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wall.sli.do/event/obRbSvykRMTii7BHz5Kdxj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wall.sli.do/event/5ytbGMXRey7ze9iYr2o1Gx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wall.sli.do/event/trwYxNkvGPU4wB6QdQKYUQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.jef-bayern.de</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wall.sli.do/event/tFRDNiRPzWnazRZebU57n1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wall.sli.do/event/geV2Mhwjr214EoiLePvBLu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nürnberg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wall.sli.do/event/igq3HyvzFLzkZURA7ceLCC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wall.sli.do/event/cGu8QCMc789wmmh8Vc2Fya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wall.sli.do/event/eHfbbWUUfx46oVaXFytCFZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wall.sli.do/event/dtWESWtajaF2nmnxngxbg4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wall.sli.do/event/gtxWrkTKz8if2RfFpJ69xd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coburg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wall.sli.do/event/b6mQoPvqwKCa17uuS6Sc22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wall.sli.do/event/fHohU9VobYosZy2K8FXVPh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wall.sli.do/event/dhRUhyE49F4UC9FAedAVXi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wall.sli.do/event/o7yWJ23ZFmzqN9rwmcYczJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wall.sli.do/event/w1XLLyqEiuitBt4KjfPpf1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">München</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wall.sli.do/event/sS3i53sFd3cVTSca6eFKws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wall.sli.do/event/iMc56Z4HtKsdxEV8VTexao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wall.sli.do/event/fjFdDNqHv5QMiJ78zkH6oi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wall.sli.do/event/cwkbmQJPXBrqs9n4p3pcw1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wall.sli.do/event/pAVG3Ho4iUe2jF4Fmn6CUT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="11"/>
@@ -116,7 +156,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
@@ -139,7 +179,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -147,21 +187,61 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+  <cellStyleXfs count="21">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1" applyProtection="1"/>
+  <cellXfs count="4">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Link" xfId="1" builtinId="8"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+  <cellStyles count="7">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="*unknown*" xfId="20" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -220,29 +300,13 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -284,12 +348,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -321,7 +385,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -345,7 +409,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -405,181 +469,184 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.13671875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9.3984375" customWidth="1"/>
-    <col min="2" max="2" width="47.1328125" customWidth="1"/>
-    <col min="3" max="4" width="50.1328125" customWidth="1"/>
-    <col min="5" max="5" width="47.53125" customWidth="1"/>
-    <col min="6" max="6" width="48.3984375" customWidth="1"/>
-    <col min="7" max="7" width="45.3984375" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="47.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="50.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="47.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="48.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="45.4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="F3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>20</v>
+      <c r="D4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>8</v>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>8</v>
-      </c>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="3"/>
+      <c r="C6" s="0"/>
+      <c r="D6" s="0"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="C2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D2" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="F2" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="G2" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="B3" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="C3" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D3" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="E3" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="F3" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="B2" r:id="rId1" display="https://wall.sli.do/event/obRbSvykRMTii7BHz5Kdxj"/>
+    <hyperlink ref="C2" r:id="rId2" display="https://wall.sli.do/event/5ytbGMXRey7ze9iYr2o1Gx"/>
+    <hyperlink ref="D2" r:id="rId3" display="https://wall.sli.do/event/trwYxNkvGPU4wB6QdQKYUQ"/>
+    <hyperlink ref="F2" r:id="rId4" display="https://wall.sli.do/event/tFRDNiRPzWnazRZebU57n1"/>
+    <hyperlink ref="G2" r:id="rId5" display="https://wall.sli.do/event/geV2Mhwjr214EoiLePvBLu"/>
+    <hyperlink ref="B3" r:id="rId6" display="https://wall.sli.do/event/igq3HyvzFLzkZURA7ceLCC"/>
+    <hyperlink ref="C3" r:id="rId7" display="https://wall.sli.do/event/cGu8QCMc789wmmh8Vc2Fya"/>
+    <hyperlink ref="D3" r:id="rId8" display="https://wall.sli.do/event/eHfbbWUUfx46oVaXFytCFZ"/>
+    <hyperlink ref="E3" r:id="rId9" display="https://wall.sli.do/event/dtWESWtajaF2nmnxngxbg4"/>
+    <hyperlink ref="F3" r:id="rId10" display="https://wall.sli.do/event/gtxWrkTKz8if2RfFpJ69xd"/>
+    <hyperlink ref="G3" r:id="rId11" display="https://wall.sli.do/event/dtWESWtajaF2nmnxngxbg4"/>
+    <hyperlink ref="B4" r:id="rId12" display="https://wall.sli.do/event/b6mQoPvqwKCa17uuS6Sc22"/>
+    <hyperlink ref="C4" r:id="rId13" display="https://wall.sli.do/event/fHohU9VobYosZy2K8FXVPh"/>
+    <hyperlink ref="D4" r:id="rId14" display="https://wall.sli.do/event/dhRUhyE49F4UC9FAedAVXi"/>
+    <hyperlink ref="E4" r:id="rId15" display="https://wall.sli.do/event/o7yWJ23ZFmzqN9rwmcYczJ"/>
+    <hyperlink ref="F4" r:id="rId16" display="https://wall.sli.do/event/w1XLLyqEiuitBt4KjfPpf1"/>
+    <hyperlink ref="G4" r:id="rId17" display="https://wall.sli.do/event/o7yWJ23ZFmzqN9rwmcYczJ"/>
+    <hyperlink ref="C5" r:id="rId18" display="https://wall.sli.do/event/iMc56Z4HtKsdxEV8VTexao"/>
+    <hyperlink ref="D5" r:id="rId19" display="https://wall.sli.do/event/fjFdDNqHv5QMiJ78zkH6oi"/>
+    <hyperlink ref="E5" r:id="rId20" display="https://wall.sli.do/event/cwkbmQJPXBrqs9n4p3pcw1"/>
+    <hyperlink ref="F5" r:id="rId21" display="https://wall.sli.do/event/pAVG3Ho4iUe2jF4Fmn6CUT"/>
+    <hyperlink ref="G5" r:id="rId22" display="https://wall.sli.do/event/cwkbmQJPXBrqs9n4p3pcw1"/>
   </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>